--- a/04_DESIGN_TABLES/DesignTable_5601.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5601.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -851,24 +856,59 @@
           <t>5601-02-02-02-FG</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.405</v>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>5601-02-02-02-FG</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1/8-27 (A (1) NPTF) x 1/8-27 (A (2) NPTF) x 1/8-27 (A (3) NPTF)</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N_1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "N1 LGTH" = "0.780" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N2@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "N2 LGTH" = "0.780" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "N3 LGTH" = "0.660" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); W@HEX: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "Y FLATS" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D1@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "A1 DRILL" = "0.188" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D2@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "A2 DRILL" = "0.188" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); TAPDRILL@BORE: end library: tap drill of the -02 female NPTF port = 0.33 (gen_straight2 FPT[2] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-02-02) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A1@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other rows); = OMi WebsitePartsInfo2026 Items Side n Thread</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -879,6 +919,11 @@
       <c r="R8" t="inlineStr">
         <is>
           <t>5601-02-02-02-FG</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -888,24 +933,59 @@
           <t>5601-04-04-04-FG</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.54</v>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>5601-04-04-04-FG</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1/4-18 (A (1) NPTF) x 1/4-18 (A (2) NPTF) x 1/4-18 (A (3) NPTF)</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5601-04-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5601-04-04-04 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N_1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "N1 LGTH" = "1.09" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N2@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "N2 LGTH" = "1.09" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "N3 LGTH" = "0.88" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); W@HEX: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "Y FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D1@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "A1 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D2@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "A2 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); TAPDRILL@BORE: end library: tap drill of the -04 female NPTF port = 0.43 (gen_straight2 FPT[4] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-03-04) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A1@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other rows); = OMi WebsitePartsInfo2026 Items Side n Thread</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5601-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5601-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5601-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -916,6 +996,11 @@
       <c r="R9" t="inlineStr">
         <is>
           <t>5601-04-04-04-FG</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -962,24 +1047,59 @@
           <t>5601-20-20-20-FG</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.66</v>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>5601-20-20-20-FG</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 (A (1) NPTF) x 1 1/4-11 1/2 (A (2) NPTF) x 1 1/4-11 1/2 (A (3) NPTF)</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N_1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-20-20-20-FG col "N1 LGTH" = "2.38" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 277.2, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N2@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-20-20-20-FG col "N2 LGTH" = "2.38" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 277.2, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-20-20-20-FG col "N3 LGTH" = "1.70" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 277.2, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); W@HEX: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-20-20-20-FG col "Y FLATS" = "1.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 277.2, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D1@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-20-20-20-FG col "A1 DRILL" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 277.2, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D2@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-20-20-20-FG col "A2 DRILL" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 277.2, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); TAPDRILL@BORE: end library: tap drill of the -20 female NPTF port = 1.48 (gen_straight2 FPT[20] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-16-20) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A1@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other rows); = OMi WebsitePartsInfo2026 Items Side n Thread</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -990,6 +1110,11 @@
       <c r="R11" t="inlineStr">
         <is>
           <t>5601-20-20-20-FG</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1027,6 +1152,237 @@
       <c r="R12" t="inlineStr">
         <is>
           <t>5601-24-24-24-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5601-08-08-08-FG</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5601-08-08-08-FG</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1/2-14 (A (1) NPTF) x 1/2-14 (A (2) NPTF) x 1/2-14 (A (3) NPTF)</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / flats / drills from the Brennan TFA catalog p.55; tap drill = Air-Way per size (A1); NPTF majors ASME</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.55 alone; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>5601-08-08-08-FG</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>5601-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5601-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3/4-14 (A (1) NPTF) x 3/4-14 (A (2) NPTF) x 3/4-14 (A (3) NPTF)</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / flats / drills from the Brennan TFA catalog p.55; tap drill = Air-Way per size (A1); NPTF majors ASME</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.55 alone; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>5601-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5601-16-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5601-16-16-16-FG</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1-11 1/2 (A (1) NPTF) x 1-11 1/2 (A (2) NPTF) x 1-11 1/2 (A (3) NPTF)</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / flats / drills from the Brennan TFA catalog p.55; tap drill = Air-Way per size (A1); NPTF majors ASME</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.55 alone; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>5601-16-16-16-FG</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_5601.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5601.xlsx
@@ -1010,24 +1010,59 @@
           <t>5601-06-06-06-FG</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.675</v>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>5601-06-06-06-FG</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3/8-18 (A (1) NPTF) x 3/8-18 (A (2) NPTF) x 3/8-18 (A (3) NPTF)</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5601-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-21] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5601-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-21 (batch 19 C, staged): Brennan allowed (user 2026-10-18 "yes use brennan but still differentiate"); Air-Way prints no value for this part number, OMi's website file gives no dimension; sizes from the Brennan TFA catalog, each checked on the part's OWN Brennan STEP (09_STEP_FILES/BRENNAN_5601-06-06-06-FG.stp, every value equal to the catalog within 0.005); end details from the end library: N_1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-06-06-06-FG col "N1 LGTH" = "1.220" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 236.8, page verified True) [Brennan = yes 2026-10-18] - run leg 1 (male): crossing to the tip; own STEP: +X face 1.22 (C_ownstep/measure/5601-06-06-06-FG.txt (pipetee.py)); N2@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-06-06-06-FG col "N2 LGTH" = "1.220" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 236.8, page verified True) [Brennan = yes 2026-10-18] - run leg 2 (male): crossing to the tip; own STEP: -X face 1.22 (C_ownstep/measure/5601-06-06-06-FG.txt (pipetee.py)); N1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-06-06-06-FG col "N3 LGTH" = "1.020" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 236.8, page verified True) [Brennan = yes 2026-10-18] - branch (female port): crossing to the port face; own STEP: +Y face 1.02 (C_ownstep/measure/5601-06-06-06-FG.txt (pipetee.py)); W@HEX: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-06-06-06-FG col "Y FLATS" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 236.8, page verified True) [Brennan = yes 2026-10-18] - forged body flats; own STEP: A/F 0.875 on every leg (C_ownstep/measure/5601-06-06-06-FG.txt (pipetee.py)); D1@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-06-06-06-FG col "A1 DRILL" = "0.406" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 236.8, page verified True) [Brennan = yes 2026-10-18] - run leg 1 bore; own STEP: +X bore 0.406 (C_ownstep/measure/5601-06-06-06-FG.txt (pipetee.py)); D2@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-06-06-06-FG col "A2 DRILL" = "0.406" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 236.8, page verified True) [Brennan = yes 2026-10-18] - run leg 2 bore; own STEP: -X bore 0.406 (C_ownstep/measure/5601-06-06-06-FG.txt (pipetee.py)); TAPDRILL@BORE: end library: tap drill of the -06 female NPTF port = 0.57 (gen_straight2 FPT[6] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-04-06) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library] (own STEP: Brennan port drill 0.578); THDMAJ_A1@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5601-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5601-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-21 batch 19 C (staged, not shipped): filled from the Brennan TFA catalog, checked on the own STEP (tools/_out/batch19_20261021/C_ownstep/measure); marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate). Cross-check only: Air-Way 5601-6-6-6 (plain): N 1.22 / 1.22 / 1.02 W 0.88 D 0.41 / 0.41 TAPDRILL 0.57 (agrees to rounding)</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1038,6 +1073,11 @@
       <c r="R10" t="inlineStr">
         <is>
           <t>5601-06-06-06-FG</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
